--- a/artfynd/A 73932-2021 artfynd.xlsx
+++ b/artfynd/A 73932-2021 artfynd.xlsx
@@ -717,7 +717,7 @@
         <v>405659</v>
       </c>
       <c r="R2" t="n">
-        <v>6409458</v>
+        <v>6409457</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>

--- a/artfynd/A 73932-2021 artfynd.xlsx
+++ b/artfynd/A 73932-2021 artfynd.xlsx
@@ -717,7 +717,7 @@
         <v>405659</v>
       </c>
       <c r="R2" t="n">
-        <v>6409457</v>
+        <v>6409458</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>

--- a/artfynd/A 73932-2021 artfynd.xlsx
+++ b/artfynd/A 73932-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AY3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,6 +780,113 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
+    <row r="3">
+      <c r="A3" t="n">
+        <v>134015692</v>
+      </c>
+      <c r="B3" t="n">
+        <v>101425</v>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E3" t="n">
+        <v>224913</v>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Vanlig backsippa</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Pulsatilla vulgaris subsp. vulgaris</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr"/>
+      <c r="I3" t="inlineStr"/>
+      <c r="J3" t="inlineStr"/>
+      <c r="K3" t="inlineStr"/>
+      <c r="L3" t="inlineStr"/>
+      <c r="N3" t="inlineStr"/>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>VIST kyrka, 400 m NO om, Vg</t>
+        </is>
+      </c>
+      <c r="Q3" t="n">
+        <v>405659</v>
+      </c>
+      <c r="R3" t="n">
+        <v>6409457</v>
+      </c>
+      <c r="S3" t="n">
+        <v>10</v>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>Västra Götaland</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>Ulricehamn</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>Västergötland</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>Ulricehamn</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>OV-Ulr-0213</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
+          <t>2026-05-22</t>
+        </is>
+      </c>
+      <c r="AD3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF3" t="inlineStr"/>
+      <c r="AG3" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT3" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>Martin Johnson</t>
+        </is>
+      </c>
+      <c r="AX3" t="inlineStr">
+        <is>
+          <t>Lars Berglund</t>
+        </is>
+      </c>
+      <c r="AY3" t="inlineStr">
+        <is>
+          <t>Floraväkteri Sverige</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 73932-2021 artfynd.xlsx
+++ b/artfynd/A 73932-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -780,113 +780,6 @@
       </c>
       <c r="AY2" t="inlineStr"/>
     </row>
-    <row r="3">
-      <c r="A3" t="n">
-        <v>134015692</v>
-      </c>
-      <c r="B3" t="n">
-        <v>101425</v>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>VU</t>
-        </is>
-      </c>
-      <c r="E3" t="n">
-        <v>224913</v>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>Vanlig backsippa</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>Pulsatilla vulgaris subsp. vulgaris</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
-      <c r="J3" t="inlineStr"/>
-      <c r="K3" t="inlineStr"/>
-      <c r="L3" t="inlineStr"/>
-      <c r="N3" t="inlineStr"/>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>VIST kyrka, 400 m NO om, Vg</t>
-        </is>
-      </c>
-      <c r="Q3" t="n">
-        <v>405659</v>
-      </c>
-      <c r="R3" t="n">
-        <v>6409457</v>
-      </c>
-      <c r="S3" t="n">
-        <v>10</v>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>Västra Götaland</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>Ulricehamn</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>Västergötland</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>Ulricehamn</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>OV-Ulr-0213</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>2026-05-22</t>
-        </is>
-      </c>
-      <c r="AD3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AF3" t="inlineStr"/>
-      <c r="AG3" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT3" t="inlineStr"/>
-      <c r="AW3" t="inlineStr">
-        <is>
-          <t>Martin Johnson</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>Lars Berglund</t>
-        </is>
-      </c>
-      <c r="AY3" t="inlineStr">
-        <is>
-          <t>Floraväkteri Sverige</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 73932-2021 artfynd.xlsx
+++ b/artfynd/A 73932-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY2"/>
+  <dimension ref="A1:AZ2"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -670,6 +670,11 @@
       <c r="AY1" t="inlineStr">
         <is>
           <t>Projektnamn</t>
+        </is>
+      </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
         </is>
       </c>
     </row>
@@ -779,8 +784,16 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133855697</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>